--- a/Bug_Report.xlsx
+++ b/Bug_Report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t xml:space="preserve">Bug ID</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Reasone</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-home-001</t>
+    <t xml:space="preserve">BUG-001</t>
   </si>
   <si>
     <t xml:space="preserve">Application accepts whitespace-only name on home page</t>
@@ -108,146 +108,37 @@
     <t xml:space="preserve">BUG-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Incorrect total in shopping cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The total price is miscalculated when multiple discounts apply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add 2 discounted items to cart
-2. Apply coupon
-3. Check total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total should reflect combined discount correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total is higher than expected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical</t>
+    <t xml:space="preserve">Hero pizza image on home page is broken (invalid URL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The &lt;img&gt; element exists in the DOM, but the image does not load and appears as a broken image icon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the home page.
+2. Locate the main hero pizza image.
+3. Observe the displayed image or broken-image icon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hero pizza image should load successfully from a valid URL.
+- The user should see the pizza picture without any broken-image icons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero pizza image element exists, but the browser shows a broken-image icon.</t>
   </si>
   <si>
     <t xml:space="preserve">In progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Hagar Ahmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salma Hassan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08-Nov-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seems related to coupon logic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing validation for email field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email field accepts invalid format without warning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Go to sign-up page
-2. Enter 'abc123' in email field
-3. Click Submit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System should show 'Invalid email' message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form accepts invalid email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Omar Ahmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07-Nov-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No validation logic found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case is not valid , old version of system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App crashes on clicking 'Generate Report'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clicking 'Generate Report' causes crash when no data is selected.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Reports tab
-2. Leave filters empty
-3. Click 'Generate Report'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System should show 'No data available' message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App crashes to home screen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06-Nov-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed in version 1.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slow loading of dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard takes too long to load after login.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login with valid credentials
-2. Wait for dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard should load within 3 seconds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Takes over 10 seconds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Salem</t>
+    <t xml:space="preserve">Test Team</t>
   </si>
   <si>
     <t xml:space="preserve">Backend Team</t>
   </si>
   <si>
-    <t xml:space="preserve">09-Nov-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performance issue under investigation</t>
+    <t xml:space="preserve">22-Nov-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image URL appears to be invalid or expired. </t>
   </si>
 </sst>
 </file>
@@ -257,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +195,19 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -386,77 +290,101 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -772,7 +700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="121.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
@@ -830,47 +758,47 @@
       <c r="M3" s="11"/>
       <c r="N3" s="12"/>
     </row>
-    <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="14" t="s">
+      <c r="J4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="K4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="L4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="M4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="15"/>
+      <c r="N4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10"/>
@@ -888,159 +816,85 @@
       <c r="M5" s="11"/>
       <c r="N5" s="12"/>
     </row>
-    <row r="6" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>49</v>
-      </c>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="15"/>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="20"/>
     </row>
-    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="N10" s="9"/>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="23"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Bug_Report.xlsx
+++ b/Bug_Report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t xml:space="preserve">Bug ID</t>
   </si>
@@ -74,7 +74,7 @@
   </si>
   <si>
     <t xml:space="preserve">1. Open the home page.
-2. In the name input field, type only spaces (e.g. "    ").
+2. In the name input field, type only spaces.
 3. Check if the "Start ordering" button appears.
 4. Click the "Start ordering" button.
 </t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Hero pizza image element exists, but the browser shows a broken-image icon.</t>
   </si>
   <si>
-    <t xml:space="preserve">In progress</t>
+    <t xml:space="preserve">Resolved</t>
   </si>
   <si>
     <t xml:space="preserve">Test Team</t>
@@ -138,17 +138,96 @@
     <t xml:space="preserve">22-Nov-2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Image URL appears to be invalid or expired. </t>
+    <t xml:space="preserve">Fixed by updating the hero image URL to a valid resource.
+Re-tested: image displays correctly and automated test passed.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer name field on order page is editable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the order page, the customer Name field is editable. 
+The user can change the name that was originally entered on the home page, 
+which violates the requirement that the customer name must remain fixed once chosen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. On the home page, enter a valid name and click "Start ordering".
+2. Add a pizza to the cart, go to the cart, then click "Order pizzas" to open the order page.
+3. Inspect the Name field on the order page.
+4. Attempt to click inside the Name field and modify its value.
+5. Try to type a different name or clear the field.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name field is read-only or disabled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name field is editable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adhm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front-end Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name input on the order page is implemented as a normal editable text field.
+Likely missing 'readonly' or 'disabled' attribute, or missing logic to prevent editing.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement breach: name should be fixed after being entered on the home page.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Get position" button on order page does not fill address field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The "Get position" feature on the order page fails to populate the address field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to the order page.
+2. Ensure the Address field is empty.
+3. Click on the "Get position" button.
+4. Wait for the result of the location/address retrieval.
+5. Check the Address field value.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After clicking "Get position", the application retrieves the user position successfully.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After clicking "Get position", the Address field remains empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely failure in geolocation or in fetching the API</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,15 +278,43 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Ubuntu"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -290,7 +397,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -347,7 +454,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -359,31 +466,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -700,7 +843,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="121.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
@@ -758,7 +901,7 @@
       <c r="M3" s="11"/>
       <c r="N3" s="12"/>
     </row>
-    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="106.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
         <v>26</v>
       </c>
@@ -816,69 +959,123 @@
       <c r="M5" s="11"/>
       <c r="N5" s="12"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="18"/>
+    <row r="6" customFormat="false" ht="225.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>45984</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="22" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="20"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="24"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="22"/>
+    <row r="8" customFormat="false" ht="166.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>45984</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="29"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17"/>
@@ -894,7 +1091,7 @@
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
-      <c r="N10" s="23"/>
+      <c r="N10" s="32"/>
     </row>
   </sheetData>
   <dataValidations count="2">
